--- a/data/defenses.xlsx
+++ b/data/defenses.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Awareness" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Evade" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Guard" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Endure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Awareness" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evade" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endure" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>don't be there • Give Ground posture</t>
+          <t>don't be there • Void Reaction and Give Ground Posture</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>don't let it through • Set Your Feet posture</t>
+          <t>don't let it through • Parry Reaction and Set Your Feet Posture</t>
         </is>
       </c>
     </row>
@@ -666,16 +666,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in Awareness: add this Constellation's Proficiency Bonus to your Awareness checks, and to your Awareness Threshold (the number Sneak, Feint, and Lie attempts are measured against). Initiative is usually an Awareness check.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>You are Trained in Awareness: add this Constellation's Proficiency Bonus to your Awareness checks, and to your Awareness Threshold (the number Sneak, Feint, and Lie attempts are measured against). Initiative is usually an Awareness check. Awareness answers Blights and Beguilement (see Chapter 2: The Four Threats).</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -688,21 +688,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Awareness Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Once per encounter, after you roll a Defense but before the outcome is announced, you may add your Wits to that roll.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -715,21 +715,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Awareness Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>When a creature critically fails to Feint against you, Lie to you, or Sneak past you, it becomes Exposed (Head) until it Recenters.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -742,21 +742,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Awareness Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>When you roll initiative and are not surprised, you may swap your place in the order with one willing ally.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -769,21 +769,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Awareness Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>The first time each encounter that a hidden or unnoticed creature attacks you, you may use Guard against that attack even though you were unaware of it.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -873,19 +873,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in Evade: add this Constellation's Proficiency Bonus to your Evade checks. It is the number attack rolls are measured against when you try to slip a blow, and the check you roll against area effects, traps, and hazards.
-You gain the Give Ground ↺ posture:
-You gain a +2 circumstance bonus to Evade for the triggering attack.
-A Zone of your choice becomes Exposed immediately, win or lose.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You are Trained in Evade: add this Constellation's Proficiency Bonus to your Evade checks. It is the number attack rolls are measured against when you try to slip a blow, and the check you roll against area effects, traps, and hazards. Evade answers Blows and Blasts.
+You gain the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Void ❶↺</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Reaction, and the Give Ground ⓿↺ Posture:
+You gain a +2 Situation bonus to Evade for the triggering attack.
+A Zone of your choice becomes Exposed until the end of the round, win or lose.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -898,21 +911,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Evade Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Your Speed increases by 5 feet while your Load Strain is 1 or less.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Your Speed increases by 1 foot while your Load Strain is 1 or less.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -925,26 +938,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Evade Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Your Steps ignore difficult terrain.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Slip the Line ↺</t>
+          <t>Slip the Line ⓿↺</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -952,26 +965,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Evade Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>(posture) +2 to your Evade against one attack. If the blow does not Hit, you end in any square adjacent to the attacker, your choice.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Posture +2 to your Evade against one attack. If the blow does not Hit, you end in any square adjacent to the attacker, your choice.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Drop Flat ↺</t>
+          <t>Drop Flat ⓿↺</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -979,21 +992,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Evade Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>(posture) +4 to your Evade against every attack until the start of your next turn. You end prone.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>Posture +4 to your Evade against every attack until your next Opportunity. You end prone.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1006,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1083,24 +1096,37 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in Guard: add this Constellation's Proficiency Bonus to your Guard checks. It is the number attack rolls are measured against when you meet a blow with weapon, shield, or braced arm, and the check you roll against fear, charm, confusion, and other assaults on your composure.
-You gain the Set Your Feet ↺ posture:
-You gain a +2 circumstance bonus to Guard for the triggering attack.
-A Zone of your choice becomes Exposed immediately, win or lose.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You are Trained in Guard: add this Constellation's Proficiency Bonus to your Guard checks. It is the number attack rolls are measured against when you meet a blow with weapon, shield, or braced arm, and the check you roll against fear, charm, confusion, and other assaults on your composure. Guard answers Blows and Beguilement, and answers a ranged Blow only with a shield Raised.
+You gain the </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Parry ❶↺</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Reaction, and the Set Your Feet ⓿↺ Posture:
+You gain a +2 Situation bonus to Guard for the triggering attack.
+A Zone of your choice becomes Exposed until the end of the round, win or lose.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Kneel Behind the Shield ↺</t>
+          <t>Catch the Blade ⓿↺</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1108,27 +1134,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Guard Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>(posture) You must have a shield Raised.
-+4 to your Guard against every attack until the start of your next turn. Your Arms become Exposed, and your Speed is 0 until you spend an action to rise.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Posture +2 to your Guard against one melee attack made with a weapon or natural weapon you could Bind. If the blow does not Hit, you take Control of the attacking weapon as though you had Parried. A Zone of your choice becomes Exposed until the end of the round, win or lose.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Unshaken</t>
+          <t>Kneel Behind the Shield ⓿↺</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1136,26 +1161,27 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Guard Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>The first time each encounter that a Graze would Expose a zone on you, it does not.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Posture You must have a shield Raised.
++4 to your Guard against every attack until your next Opportunity. Your Arms become Exposed, and your Speed is 0 until you spend an action to rise.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Deflecting Palms ↺</t>
+          <t>Unshaken</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1163,27 +1189,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Guard Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Trigger You are hit and have a hand free.
-Effect Reduce that attack's damage by 2 plus your Presence.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>The first time each encounter that you take a Posture, it Exposes nothing.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Cover the Angle ↺</t>
+          <t>Deflecting Palms ❶↺</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1191,54 +1216,134 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Guard Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Trigger An adjacent ally is attacked.
-Effect The attack is measured against your Guard instead of their chosen Defense, and any Graze cost falls on you.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are hit and have a hand free.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Reduce that attack's damage by 2 plus your Presence.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Cover the Angle ❶↺</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Guard Training</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> An adjacent ally is attacked.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> The attack is measured against your Guard instead of their chosen Defense, and any Bind that forms is with your weapon or shield.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Larger than Life</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Guard Training</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Requirements You are wearing Plate in all Zones.
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wearing Plate in all Zones.
 Though you don't get any larger, you're treated as one size larger for the purposes of affecting other creatures with actions like Disarm, Grapple, Reposition, Shove, and Trip while wearing heavy armor. Similarly, you're treated as one size larger for the purposes of creatures affecting you with those same actions, as well as with Swallow Whole and similar actions, while wearing heavy armor.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1328,16 +1433,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in Endure: add this Constellation's Proficiency Bonus to your Endure checks. It is the check you roll against poison, disease, exhaustion, and anything trying to break your body. You also reduce your Load Strain by 1 (to a minimum of 0) once you reach Expert rank, 2 at Master, and 3 at Legendary.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>You are Trained in Endure: add this Constellation's Proficiency Bonus to your Endure checks. It is the check you roll against poison, disease, exhaustion, and anything trying to break your body. Endure answers Blasts and Blights. You also reduce your Load Strain by 1 (to a minimum of 0) once you reach Expert rank, 2 at Master, and 3 at Legendary.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,26 +1455,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Endure Training</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Reduce each instance of persistent damage you take by your Might. This can never reduce it below 1.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Second Wind ◆◆</t>
+          <t>Second Wind ❷</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1377,21 +1482,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Endure Training</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Once per day, dig deep: regain Hit Points equal to half your level plus your Might.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Once per day, dig deep: regain Vigor equal to half your level plus your Might.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1404,26 +1509,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Endure Training</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2 circumstance bonus to your Guard against Shove, Trip, and Reposition.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>+2 Situation bonus to your Guard against Shove, Trip, and Reposition.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Blade Brake ↺</t>
+          <t>Blade Brake ❶↺</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1431,23 +1536,44 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Endure Training</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Trigger You would be moved by a forced movement effect.
-Requirements You are wielding a melee weapon and are within reach of a hard surface.
-You plow your weapon into a floor, wall, or another sturdy surface, anchoring yourself in place. If you would be moved 20 feet or more, you are moved only 5 feet. Otherwise, you don't move at all.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You would be moved by a forced movement effect
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You are wielding a melee weapon and are within reach of a hard surface
+You plow your weapon into a floor, wall, or another sturdy surface, anchoring yourself in place. If you would be moved 6 feet or more, you are moved only 1 foot. Otherwise, you don't move at all.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/defenses.xlsx
+++ b/data/defenses.xlsx
@@ -1542,7 +1542,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You are Trained in Endure: add this Constellation's Proficiency Bonus to your Endure checks. It is the check you roll against poison, disease, exhaustion, and anything trying to break your body. Endure answers Blasts and Blights. You also reduce your Load Strain by 1 (to a minimum of 0) once you reach Expert rank, 2 at Master, and 3 at Legendary.</t>
+          <t>You are Trained in Endure: add this Constellation's Proficiency Bonus to your Endure checks. It is the check you roll against poison, disease, exhaustion, and anything trying to break your body. Endure answers Blasts and Blights. You also reduce your Load Strain by 1 (to a minimum of 0) at Trained, 2 at Expert, 3 at Master, and 4 at Legendary. Your Vigor grows with your conditioning as well: at Expert rank in Endure you gain 1 more Vigor at every level, 2 at Master, and 3 at Legendary.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>

--- a/data/defenses.xlsx
+++ b/data/defenses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\StarWrought\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444347EC-90C0-46B9-B981-D93FC8673486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FA2D67-DD11-409E-A2F6-8315C7190074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="6045" windowWidth="36450" windowHeight="13980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="6045" windowWidth="36450" windowHeight="13980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Tree Index" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="77">
   <si>
     <t>Talent</t>
   </si>
@@ -969,6 +969,9 @@
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
